--- a/horizon excursion/15 years - bundles as antigen (NOT DONE)/production_capacity_updated.xlsx
+++ b/horizon excursion/15 years - bundles as antigen (NOT DONE)/production_capacity_updated.xlsx
@@ -5,10 +5,10 @@
   <workbookPr hidePivotFieldList="1" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5e6b18ad1acc1266/Desktop/Vaccine_Tender/horizon excursion/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5e6b18ad1acc1266/Desktop/Vaccine_Tender/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="198" documentId="13_ncr:1_{68782C53-48E3-42CA-912A-5E0671CC39DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2B250B3A-70F5-4B82-8995-D7E281AAF57C}"/>
+  <xr:revisionPtr revIDLastSave="155" documentId="13_ncr:1_{68782C53-48E3-42CA-912A-5E0671CC39DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0E313997-B984-44EE-A796-E33C8848E5C0}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="1" activeTab="4" xr2:uid="{752E71BE-3FD4-4CCA-ABF0-6C5710D300B4}"/>
   </bookViews>
@@ -18,7 +18,6 @@
     <sheet name="Prod_capacity_agg" sheetId="9" r:id="rId3"/>
     <sheet name="Producers_short_name" sheetId="5" r:id="rId4"/>
     <sheet name="Medium_Capacity" sheetId="6" r:id="rId5"/>
-    <sheet name="Sheet1" sheetId="10" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Medium_Capacity!$A$2:$O$18</definedName>
@@ -31,7 +30,7 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="0" r:id="rId7"/>
+    <pivotCache cacheId="0" r:id="rId6"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -189,7 +188,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="757" uniqueCount="172">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="760" uniqueCount="175">
   <si>
     <t>Vaccine</t>
   </si>
@@ -701,6 +700,15 @@
     <t>Sum of 10</t>
   </si>
   <si>
+    <t>Medium Cap</t>
+  </si>
+  <si>
+    <t>Low Cap</t>
+  </si>
+  <si>
+    <t>High Cap</t>
+  </si>
+  <si>
     <t>Producer X</t>
   </si>
   <si>
@@ -711,9 +719,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="165" formatCode="0.0000E+00"/>
   </numFmts>
   <fonts count="11" x14ac:knownFonts="1">
     <font>
@@ -948,7 +957,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -1020,6 +1029,7 @@
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="4" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1035,6 +1045,9 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -2387,7 +2400,7 @@
         <v>156</v>
       </c>
       <c r="T1" s="33" t="s">
-        <v>170</v>
+        <v>154</v>
       </c>
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.25">
@@ -3681,7 +3694,7 @@
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A2" s="43" t="s">
+      <c r="A2" s="44" t="s">
         <v>12</v>
       </c>
       <c r="B2" s="4" t="s">
@@ -3699,7 +3712,7 @@
       <c r="L2" s="6"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" s="43" t="s">
+      <c r="A3" s="44" t="s">
         <v>12</v>
       </c>
       <c r="B3" s="4" t="s">
@@ -3737,7 +3750,7 @@
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A4" s="43" t="s">
+      <c r="A4" s="44" t="s">
         <v>12</v>
       </c>
       <c r="B4" s="4" t="s">
@@ -3775,7 +3788,7 @@
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A5" s="43" t="s">
+      <c r="A5" s="44" t="s">
         <v>12</v>
       </c>
       <c r="B5" s="4" t="s">
@@ -3813,7 +3826,7 @@
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A6" s="43" t="s">
+      <c r="A6" s="44" t="s">
         <v>12</v>
       </c>
       <c r="B6" s="4" t="s">
@@ -3851,7 +3864,7 @@
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A7" s="43" t="s">
+      <c r="A7" s="44" t="s">
         <v>18</v>
       </c>
       <c r="B7" s="4" t="s">
@@ -3881,7 +3894,7 @@
       <c r="L7" s="6"/>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A8" s="43" t="s">
+      <c r="A8" s="44" t="s">
         <v>18</v>
       </c>
       <c r="B8" s="4" t="s">
@@ -3911,7 +3924,7 @@
       <c r="L8" s="6"/>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A9" s="43" t="s">
+      <c r="A9" s="44" t="s">
         <v>18</v>
       </c>
       <c r="B9" s="4" t="s">
@@ -3941,7 +3954,7 @@
       <c r="L9" s="6"/>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A10" s="43" t="s">
+      <c r="A10" s="44" t="s">
         <v>18</v>
       </c>
       <c r="B10" s="4" t="s">
@@ -3971,7 +3984,7 @@
       <c r="L10" s="6"/>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A11" s="43" t="s">
+      <c r="A11" s="44" t="s">
         <v>19</v>
       </c>
       <c r="B11" s="4" t="s">
@@ -4009,7 +4022,7 @@
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A12" s="43" t="s">
+      <c r="A12" s="44" t="s">
         <v>19</v>
       </c>
       <c r="B12" s="4" t="s">
@@ -4047,7 +4060,7 @@
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A13" s="43" t="s">
+      <c r="A13" s="44" t="s">
         <v>19</v>
       </c>
       <c r="B13" s="4" t="s">
@@ -4085,7 +4098,7 @@
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A14" s="43" t="s">
+      <c r="A14" s="44" t="s">
         <v>19</v>
       </c>
       <c r="B14" s="4" t="s">
@@ -4159,7 +4172,7 @@
       <c r="L16" s="6"/>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A17" s="43" t="s">
+      <c r="A17" s="44" t="s">
         <v>22</v>
       </c>
       <c r="B17" s="4" t="s">
@@ -4177,7 +4190,7 @@
       <c r="L17" s="6"/>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A18" s="43" t="s">
+      <c r="A18" s="44" t="s">
         <v>22</v>
       </c>
       <c r="B18" s="4" t="s">
@@ -4215,7 +4228,7 @@
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A19" s="43" t="s">
+      <c r="A19" s="44" t="s">
         <v>22</v>
       </c>
       <c r="B19" s="4" t="s">
@@ -4253,7 +4266,7 @@
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A20" s="43" t="s">
+      <c r="A20" s="44" t="s">
         <v>22</v>
       </c>
       <c r="B20" s="4" t="s">
@@ -4291,7 +4304,7 @@
       </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A21" s="43" t="s">
+      <c r="A21" s="44" t="s">
         <v>22</v>
       </c>
       <c r="B21" s="4" t="s">
@@ -4329,7 +4342,7 @@
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A22" s="43" t="s">
+      <c r="A22" s="44" t="s">
         <v>23</v>
       </c>
       <c r="B22" s="4" t="s">
@@ -4347,7 +4360,7 @@
       <c r="L22" s="6"/>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A23" s="43" t="s">
+      <c r="A23" s="44" t="s">
         <v>23</v>
       </c>
       <c r="B23" s="4" t="s">
@@ -4385,7 +4398,7 @@
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A24" s="43" t="s">
+      <c r="A24" s="44" t="s">
         <v>23</v>
       </c>
       <c r="B24" s="4" t="s">
@@ -4403,7 +4416,7 @@
       <c r="L24" s="6"/>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A25" s="43" t="s">
+      <c r="A25" s="44" t="s">
         <v>23</v>
       </c>
       <c r="B25" s="4" t="s">
@@ -4433,7 +4446,7 @@
       <c r="L25" s="6"/>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A26" s="43" t="s">
+      <c r="A26" s="44" t="s">
         <v>23</v>
       </c>
       <c r="B26" s="4" t="s">
@@ -4489,7 +4502,7 @@
       <c r="L27" s="6"/>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A28" s="43" t="s">
+      <c r="A28" s="44" t="s">
         <v>25</v>
       </c>
       <c r="B28" s="4" t="s">
@@ -4527,7 +4540,7 @@
       </c>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A29" s="43" t="s">
+      <c r="A29" s="44" t="s">
         <v>25</v>
       </c>
       <c r="B29" s="4" t="s">
@@ -4557,7 +4570,7 @@
       <c r="L29" s="6"/>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A30" s="43" t="s">
+      <c r="A30" s="44" t="s">
         <v>25</v>
       </c>
       <c r="B30" s="4" t="s">
@@ -4583,7 +4596,7 @@
       </c>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A31" s="43" t="s">
+      <c r="A31" s="44" t="s">
         <v>26</v>
       </c>
       <c r="B31" s="4" t="s">
@@ -4621,7 +4634,7 @@
       </c>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A32" s="43" t="s">
+      <c r="A32" s="44" t="s">
         <v>26</v>
       </c>
       <c r="B32" s="4" t="s">
@@ -4647,7 +4660,7 @@
       <c r="L32" s="6"/>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A33" s="43" t="s">
+      <c r="A33" s="44" t="s">
         <v>26</v>
       </c>
       <c r="B33" s="4" t="s">
@@ -4685,7 +4698,7 @@
       </c>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A34" s="43" t="s">
+      <c r="A34" s="44" t="s">
         <v>27</v>
       </c>
       <c r="B34" s="4" t="s">
@@ -4723,7 +4736,7 @@
       </c>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A35" s="43" t="s">
+      <c r="A35" s="44" t="s">
         <v>27</v>
       </c>
       <c r="B35" s="4" t="s">
@@ -4753,7 +4766,7 @@
       <c r="L35" s="6"/>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A36" s="43" t="s">
+      <c r="A36" s="44" t="s">
         <v>27</v>
       </c>
       <c r="B36" s="4" t="s">
@@ -4779,7 +4792,7 @@
       </c>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A37" s="43" t="s">
+      <c r="A37" s="44" t="s">
         <v>28</v>
       </c>
       <c r="B37" s="4" t="s">
@@ -4817,7 +4830,7 @@
       </c>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A38" s="43" t="s">
+      <c r="A38" s="44" t="s">
         <v>28</v>
       </c>
       <c r="B38" s="4" t="s">
@@ -4843,7 +4856,7 @@
       <c r="L38" s="6"/>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A39" s="43" t="s">
+      <c r="A39" s="44" t="s">
         <v>29</v>
       </c>
       <c r="B39" s="4" t="s">
@@ -4881,7 +4894,7 @@
       </c>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A40" s="43" t="s">
+      <c r="A40" s="44" t="s">
         <v>29</v>
       </c>
       <c r="B40" s="4" t="s">
@@ -4907,7 +4920,7 @@
       <c r="L40" s="6"/>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A41" s="43" t="s">
+      <c r="A41" s="44" t="s">
         <v>29</v>
       </c>
       <c r="B41" s="4" t="s">
@@ -4945,7 +4958,7 @@
       </c>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A42" s="43" t="s">
+      <c r="A42" s="44" t="s">
         <v>30</v>
       </c>
       <c r="B42" s="4" t="s">
@@ -4983,7 +4996,7 @@
       </c>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A43" s="43" t="s">
+      <c r="A43" s="44" t="s">
         <v>30</v>
       </c>
       <c r="B43" s="4" t="s">
@@ -5001,7 +5014,7 @@
       <c r="L43" s="6"/>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A44" s="43" t="s">
+      <c r="A44" s="44" t="s">
         <v>30</v>
       </c>
       <c r="B44" s="4" t="s">
@@ -5039,7 +5052,7 @@
       </c>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A45" s="43" t="s">
+      <c r="A45" s="44" t="s">
         <v>31</v>
       </c>
       <c r="B45" s="4" t="s">
@@ -5057,7 +5070,7 @@
       <c r="L45" s="6"/>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A46" s="43" t="s">
+      <c r="A46" s="44" t="s">
         <v>31</v>
       </c>
       <c r="B46" s="4" t="s">
@@ -5095,7 +5108,7 @@
       </c>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A47" s="43" t="s">
+      <c r="A47" s="44" t="s">
         <v>31</v>
       </c>
       <c r="B47" s="4" t="s">
@@ -5133,7 +5146,7 @@
       </c>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A48" s="43" t="s">
+      <c r="A48" s="44" t="s">
         <v>31</v>
       </c>
       <c r="B48" s="4" t="s">
@@ -5171,7 +5184,7 @@
       </c>
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A49" s="43" t="s">
+      <c r="A49" s="44" t="s">
         <v>31</v>
       </c>
       <c r="B49" s="4" t="s">
@@ -5209,7 +5222,7 @@
       </c>
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A50" s="43" t="s">
+      <c r="A50" s="44" t="s">
         <v>32</v>
       </c>
       <c r="B50" s="4" t="s">
@@ -5227,7 +5240,7 @@
       <c r="L50" s="6"/>
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A51" s="43" t="s">
+      <c r="A51" s="44" t="s">
         <v>32</v>
       </c>
       <c r="B51" s="4" t="s">
@@ -5245,7 +5258,7 @@
       <c r="L51" s="6"/>
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A52" s="43" t="s">
+      <c r="A52" s="44" t="s">
         <v>32</v>
       </c>
       <c r="B52" s="4" t="s">
@@ -5263,7 +5276,7 @@
       <c r="L52" s="6"/>
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A53" s="43" t="s">
+      <c r="A53" s="44" t="s">
         <v>32</v>
       </c>
       <c r="B53" s="4" t="s">
@@ -5301,7 +5314,7 @@
       </c>
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A54" s="43" t="s">
+      <c r="A54" s="44" t="s">
         <v>33</v>
       </c>
       <c r="B54" s="4" t="s">
@@ -5339,7 +5352,7 @@
       </c>
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A55" s="43" t="s">
+      <c r="A55" s="44" t="s">
         <v>33</v>
       </c>
       <c r="B55" s="4" t="s">
@@ -5377,7 +5390,7 @@
       </c>
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A56" s="43" t="s">
+      <c r="A56" s="44" t="s">
         <v>33</v>
       </c>
       <c r="B56" s="4" t="s">
@@ -5415,7 +5428,7 @@
       </c>
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A57" s="43" t="s">
+      <c r="A57" s="44" t="s">
         <v>33</v>
       </c>
       <c r="B57" s="4" t="s">
@@ -5453,7 +5466,7 @@
       </c>
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A58" s="43" t="s">
+      <c r="A58" s="44" t="s">
         <v>34</v>
       </c>
       <c r="B58" s="4" t="s">
@@ -5491,7 +5504,7 @@
       </c>
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A59" s="43" t="s">
+      <c r="A59" s="44" t="s">
         <v>34</v>
       </c>
       <c r="B59" s="4" t="s">
@@ -5529,7 +5542,7 @@
       </c>
     </row>
     <row r="60" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A60" s="43" t="s">
+      <c r="A60" s="44" t="s">
         <v>34</v>
       </c>
       <c r="B60" s="4" t="s">
@@ -5567,7 +5580,7 @@
       </c>
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A61" s="43" t="s">
+      <c r="A61" s="44" t="s">
         <v>34</v>
       </c>
       <c r="B61" s="4" t="s">
@@ -5587,7 +5600,7 @@
       <c r="L61" s="6"/>
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A62" s="43" t="s">
+      <c r="A62" s="44" t="s">
         <v>35</v>
       </c>
       <c r="B62" s="4" t="s">
@@ -5625,7 +5638,7 @@
       </c>
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A63" s="43" t="s">
+      <c r="A63" s="44" t="s">
         <v>35</v>
       </c>
       <c r="B63" s="4" t="s">
@@ -5663,7 +5676,7 @@
       </c>
     </row>
     <row r="64" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A64" s="43" t="s">
+      <c r="A64" s="44" t="s">
         <v>35</v>
       </c>
       <c r="B64" s="4" t="s">
@@ -5701,7 +5714,7 @@
       </c>
     </row>
     <row r="65" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A65" s="43" t="s">
+      <c r="A65" s="44" t="s">
         <v>36</v>
       </c>
       <c r="B65" s="4" t="s">
@@ -5719,7 +5732,7 @@
       <c r="L65" s="6"/>
     </row>
     <row r="66" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A66" s="43" t="s">
+      <c r="A66" s="44" t="s">
         <v>36</v>
       </c>
       <c r="B66" s="4" t="s">
@@ -5757,7 +5770,7 @@
       </c>
     </row>
     <row r="67" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A67" s="43" t="s">
+      <c r="A67" s="44" t="s">
         <v>36</v>
       </c>
       <c r="B67" s="4" t="s">
@@ -5795,7 +5808,7 @@
       </c>
     </row>
     <row r="68" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A68" s="43" t="s">
+      <c r="A68" s="44" t="s">
         <v>36</v>
       </c>
       <c r="B68" s="4" t="s">
@@ -5833,7 +5846,7 @@
       </c>
     </row>
     <row r="69" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A69" s="43" t="s">
+      <c r="A69" s="44" t="s">
         <v>36</v>
       </c>
       <c r="B69" s="4" t="s">
@@ -5871,7 +5884,7 @@
       </c>
     </row>
     <row r="70" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A70" s="43" t="s">
+      <c r="A70" s="44" t="s">
         <v>37</v>
       </c>
       <c r="B70" s="4" t="s">
@@ -5889,7 +5902,7 @@
       <c r="L70" s="6"/>
     </row>
     <row r="71" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A71" s="43" t="s">
+      <c r="A71" s="44" t="s">
         <v>37</v>
       </c>
       <c r="B71" s="4" t="s">
@@ -5927,7 +5940,7 @@
       </c>
     </row>
     <row r="72" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A72" s="43" t="s">
+      <c r="A72" s="44" t="s">
         <v>37</v>
       </c>
       <c r="B72" s="4" t="s">
@@ -5945,7 +5958,7 @@
       <c r="L72" s="6"/>
     </row>
     <row r="73" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A73" s="43" t="s">
+      <c r="A73" s="44" t="s">
         <v>37</v>
       </c>
       <c r="B73" s="4" t="s">
@@ -5975,7 +5988,7 @@
       <c r="L73" s="6"/>
     </row>
     <row r="74" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A74" s="43" t="s">
+      <c r="A74" s="44" t="s">
         <v>37</v>
       </c>
       <c r="B74" s="4" t="s">
@@ -6013,7 +6026,7 @@
       </c>
     </row>
     <row r="75" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A75" s="43" t="s">
+      <c r="A75" s="44" t="s">
         <v>38</v>
       </c>
       <c r="B75" s="4" t="s">
@@ -6043,7 +6056,7 @@
       </c>
     </row>
     <row r="76" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A76" s="43" t="s">
+      <c r="A76" s="44" t="s">
         <v>38</v>
       </c>
       <c r="B76" s="4" t="s">
@@ -6107,7 +6120,7 @@
       </c>
     </row>
     <row r="78" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A78" s="43" t="s">
+      <c r="A78" s="44" t="s">
         <v>40</v>
       </c>
       <c r="B78" s="4" t="s">
@@ -6145,7 +6158,7 @@
       </c>
     </row>
     <row r="79" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A79" s="43" t="s">
+      <c r="A79" s="44" t="s">
         <v>40</v>
       </c>
       <c r="B79" s="4" t="s">
@@ -6183,7 +6196,7 @@
       </c>
     </row>
     <row r="80" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A80" s="43" t="s">
+      <c r="A80" s="44" t="s">
         <v>40</v>
       </c>
       <c r="B80" s="4" t="s">
@@ -6221,7 +6234,7 @@
       </c>
     </row>
     <row r="81" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A81" s="43" t="s">
+      <c r="A81" s="44" t="s">
         <v>40</v>
       </c>
       <c r="B81" s="4" t="s">
@@ -6259,7 +6272,7 @@
       </c>
     </row>
     <row r="82" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A82" s="43" t="s">
+      <c r="A82" s="44" t="s">
         <v>41</v>
       </c>
       <c r="B82" s="4" t="s">
@@ -6297,7 +6310,7 @@
       </c>
     </row>
     <row r="83" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A83" s="43" t="s">
+      <c r="A83" s="44" t="s">
         <v>41</v>
       </c>
       <c r="B83" s="4" t="s">
@@ -6335,7 +6348,7 @@
       </c>
     </row>
     <row r="84" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A84" s="43" t="s">
+      <c r="A84" s="44" t="s">
         <v>41</v>
       </c>
       <c r="B84" s="4" t="s">
@@ -6373,7 +6386,7 @@
       </c>
     </row>
     <row r="85" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A85" s="43" t="s">
+      <c r="A85" s="44" t="s">
         <v>41</v>
       </c>
       <c r="B85" s="4" t="s">
@@ -6411,7 +6424,7 @@
       </c>
     </row>
     <row r="86" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A86" s="43" t="s">
+      <c r="A86" s="44" t="s">
         <v>42</v>
       </c>
       <c r="B86" s="4" t="s">
@@ -6449,7 +6462,7 @@
       </c>
     </row>
     <row r="87" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A87" s="43" t="s">
+      <c r="A87" s="44" t="s">
         <v>42</v>
       </c>
       <c r="B87" s="4" t="s">
@@ -6467,7 +6480,7 @@
       <c r="L87" s="6"/>
     </row>
     <row r="88" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A88" s="43" t="s">
+      <c r="A88" s="44" t="s">
         <v>42</v>
       </c>
       <c r="B88" s="4" t="s">
@@ -6505,7 +6518,7 @@
       </c>
     </row>
     <row r="89" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A89" s="43" t="s">
+      <c r="A89" s="44" t="s">
         <v>42</v>
       </c>
       <c r="B89" s="4" t="s">
@@ -6543,7 +6556,7 @@
       </c>
     </row>
     <row r="90" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A90" s="44" t="s">
+      <c r="A90" s="45" t="s">
         <v>43</v>
       </c>
       <c r="B90" s="4" t="s">
@@ -6561,7 +6574,7 @@
       <c r="L90" s="6"/>
     </row>
     <row r="91" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A91" s="45" t="s">
+      <c r="A91" s="46" t="s">
         <v>43</v>
       </c>
       <c r="B91" s="4" t="s">
@@ -6599,7 +6612,7 @@
       </c>
     </row>
     <row r="92" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A92" s="45" t="s">
+      <c r="A92" s="46" t="s">
         <v>43</v>
       </c>
       <c r="B92" s="4" t="s">
@@ -6637,7 +6650,7 @@
       </c>
     </row>
     <row r="93" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A93" s="45" t="s">
+      <c r="A93" s="46" t="s">
         <v>43</v>
       </c>
       <c r="B93" s="4" t="s">
@@ -6675,7 +6688,7 @@
       </c>
     </row>
     <row r="94" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A94" s="46" t="s">
+      <c r="A94" s="47" t="s">
         <v>43</v>
       </c>
       <c r="B94" s="4" t="s">
@@ -6713,7 +6726,7 @@
       </c>
     </row>
     <row r="95" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A95" s="43" t="s">
+      <c r="A95" s="44" t="s">
         <v>44</v>
       </c>
       <c r="B95" s="4" t="s">
@@ -6751,7 +6764,7 @@
       </c>
     </row>
     <row r="96" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A96" s="43" t="s">
+      <c r="A96" s="44" t="s">
         <v>44</v>
       </c>
       <c r="B96" s="4" t="s">
@@ -6789,7 +6802,7 @@
       </c>
     </row>
     <row r="97" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A97" s="43" t="s">
+      <c r="A97" s="44" t="s">
         <v>44</v>
       </c>
       <c r="B97" s="4" t="s">
@@ -6827,7 +6840,7 @@
       </c>
     </row>
     <row r="98" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A98" s="43" t="s">
+      <c r="A98" s="44" t="s">
         <v>45</v>
       </c>
       <c r="B98" s="4" t="s">
@@ -6857,7 +6870,7 @@
       </c>
     </row>
     <row r="99" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A99" s="43" t="s">
+      <c r="A99" s="44" t="s">
         <v>45</v>
       </c>
       <c r="B99" s="4" t="s">
@@ -6875,7 +6888,7 @@
       <c r="L99" s="6"/>
     </row>
     <row r="100" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A100" s="43" t="s">
+      <c r="A100" s="44" t="s">
         <v>45</v>
       </c>
       <c r="B100" s="4" t="s">
@@ -6901,7 +6914,7 @@
       <c r="L100" s="6"/>
     </row>
     <row r="101" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A101" s="43" t="s">
+      <c r="A101" s="44" t="s">
         <v>46</v>
       </c>
       <c r="B101" s="4" t="s">
@@ -6939,7 +6952,7 @@
       </c>
     </row>
     <row r="102" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A102" s="43" t="s">
+      <c r="A102" s="44" t="s">
         <v>46</v>
       </c>
       <c r="B102" s="4" t="s">
@@ -6957,7 +6970,7 @@
       <c r="L102" s="6"/>
     </row>
     <row r="103" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A103" s="43" t="s">
+      <c r="A103" s="44" t="s">
         <v>46</v>
       </c>
       <c r="B103" s="4" t="s">
@@ -6983,7 +6996,7 @@
       <c r="L103" s="6"/>
     </row>
     <row r="104" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A104" s="43" t="s">
+      <c r="A104" s="44" t="s">
         <v>47</v>
       </c>
       <c r="B104" s="4" t="s">
@@ -7013,7 +7026,7 @@
       </c>
     </row>
     <row r="105" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A105" s="43" t="s">
+      <c r="A105" s="44" t="s">
         <v>47</v>
       </c>
       <c r="B105" s="4" t="s">
@@ -7041,7 +7054,7 @@
       <c r="L105" s="6"/>
     </row>
     <row r="106" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A106" s="43" t="s">
+      <c r="A106" s="44" t="s">
         <v>47</v>
       </c>
       <c r="B106" s="4" t="s">
@@ -7077,7 +7090,7 @@
       </c>
     </row>
     <row r="107" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A107" s="43" t="s">
+      <c r="A107" s="44" t="s">
         <v>48</v>
       </c>
       <c r="B107" s="4" t="s">
@@ -7115,7 +7128,7 @@
       </c>
     </row>
     <row r="108" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A108" s="43" t="s">
+      <c r="A108" s="44" t="s">
         <v>48</v>
       </c>
       <c r="B108" s="4" t="s">
@@ -7153,7 +7166,7 @@
       </c>
     </row>
     <row r="109" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A109" s="43" t="s">
+      <c r="A109" s="44" t="s">
         <v>48</v>
       </c>
       <c r="B109" s="4" t="s">
@@ -7171,7 +7184,7 @@
       <c r="L109" s="6"/>
     </row>
     <row r="110" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A110" s="43" t="s">
+      <c r="A110" s="44" t="s">
         <v>49</v>
       </c>
       <c r="B110" s="4" t="s">
@@ -7209,7 +7222,7 @@
       </c>
     </row>
     <row r="111" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A111" s="43" t="s">
+      <c r="A111" s="44" t="s">
         <v>49</v>
       </c>
       <c r="B111" s="4" t="s">
@@ -7247,7 +7260,7 @@
       </c>
     </row>
     <row r="112" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A112" s="43" t="s">
+      <c r="A112" s="44" t="s">
         <v>49</v>
       </c>
       <c r="B112" s="4" t="s">
@@ -7283,7 +7296,7 @@
       </c>
     </row>
     <row r="113" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A113" s="43" t="s">
+      <c r="A113" s="44" t="s">
         <v>49</v>
       </c>
       <c r="B113" s="4" t="s">
@@ -7321,7 +7334,7 @@
       </c>
     </row>
     <row r="114" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A114" s="43" t="s">
+      <c r="A114" s="44" t="s">
         <v>50</v>
       </c>
       <c r="B114" s="4" t="s">
@@ -7359,7 +7372,7 @@
       </c>
     </row>
     <row r="115" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A115" s="43" t="s">
+      <c r="A115" s="44" t="s">
         <v>50</v>
       </c>
       <c r="B115" s="4" t="s">
@@ -7397,7 +7410,7 @@
       </c>
     </row>
     <row r="116" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A116" s="43" t="s">
+      <c r="A116" s="44" t="s">
         <v>50</v>
       </c>
       <c r="B116" s="4" t="s">
@@ -7435,7 +7448,7 @@
       </c>
     </row>
     <row r="117" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A117" s="43" t="s">
+      <c r="A117" s="44" t="s">
         <v>50</v>
       </c>
       <c r="B117" s="4" t="s">
@@ -7473,7 +7486,7 @@
       </c>
     </row>
     <row r="118" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A118" s="43" t="s">
+      <c r="A118" s="44" t="s">
         <v>50</v>
       </c>
       <c r="B118" s="4" t="s">
@@ -7547,7 +7560,7 @@
       </c>
     </row>
     <row r="120" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A120" s="43" t="s">
+      <c r="A120" s="44" t="s">
         <v>52</v>
       </c>
       <c r="B120" s="4" t="s">
@@ -7565,7 +7578,7 @@
       <c r="L120" s="6"/>
     </row>
     <row r="121" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A121" s="43" t="s">
+      <c r="A121" s="44" t="s">
         <v>52</v>
       </c>
       <c r="B121" s="4" t="s">
@@ -7597,7 +7610,7 @@
       </c>
     </row>
     <row r="122" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A122" s="43" t="s">
+      <c r="A122" s="44" t="s">
         <v>52</v>
       </c>
       <c r="B122" s="4" t="s">
@@ -7635,7 +7648,7 @@
       </c>
     </row>
     <row r="123" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A123" s="43" t="s">
+      <c r="A123" s="44" t="s">
         <v>53</v>
       </c>
       <c r="B123" s="4" t="s">
@@ -7673,7 +7686,7 @@
       </c>
     </row>
     <row r="124" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A124" s="43" t="s">
+      <c r="A124" s="44" t="s">
         <v>53</v>
       </c>
       <c r="B124" s="4" t="s">
@@ -7711,7 +7724,7 @@
       </c>
     </row>
     <row r="125" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A125" s="43" t="s">
+      <c r="A125" s="44" t="s">
         <v>53</v>
       </c>
       <c r="B125" s="4" t="s">
@@ -7749,7 +7762,7 @@
       </c>
     </row>
     <row r="126" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A126" s="43" t="s">
+      <c r="A126" s="44" t="s">
         <v>54</v>
       </c>
       <c r="B126" s="4" t="s">
@@ -7767,7 +7780,7 @@
       <c r="L126" s="6"/>
     </row>
     <row r="127" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A127" s="43" t="s">
+      <c r="A127" s="44" t="s">
         <v>54</v>
       </c>
       <c r="B127" s="4" t="s">
@@ -7785,7 +7798,7 @@
       <c r="L127" s="6"/>
     </row>
     <row r="128" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A128" s="43" t="s">
+      <c r="A128" s="44" t="s">
         <v>54</v>
       </c>
       <c r="B128" s="4" t="s">
@@ -7803,7 +7816,7 @@
       <c r="L128" s="6"/>
     </row>
     <row r="129" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A129" s="43" t="s">
+      <c r="A129" s="44" t="s">
         <v>54</v>
       </c>
       <c r="B129" s="4" t="s">
@@ -7823,7 +7836,7 @@
       <c r="L129" s="6"/>
     </row>
     <row r="130" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A130" s="43" t="s">
+      <c r="A130" s="44" t="s">
         <v>55</v>
       </c>
       <c r="B130" s="4" t="s">
@@ -7841,7 +7854,7 @@
       <c r="L130" s="6"/>
     </row>
     <row r="131" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A131" s="43" t="s">
+      <c r="A131" s="44" t="s">
         <v>55</v>
       </c>
       <c r="B131" s="4" t="s">
@@ -7879,7 +7892,7 @@
       </c>
     </row>
     <row r="132" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A132" s="43" t="s">
+      <c r="A132" s="44" t="s">
         <v>55</v>
       </c>
       <c r="B132" s="4" t="s">
@@ -7917,7 +7930,7 @@
       </c>
     </row>
     <row r="133" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A133" s="43" t="s">
+      <c r="A133" s="44" t="s">
         <v>55</v>
       </c>
       <c r="B133" s="4" t="s">
@@ -7955,7 +7968,7 @@
       </c>
     </row>
     <row r="134" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A134" s="43" t="s">
+      <c r="A134" s="44" t="s">
         <v>55</v>
       </c>
       <c r="B134" s="4" t="s">
@@ -7993,7 +8006,7 @@
       </c>
     </row>
     <row r="135" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A135" s="43" t="s">
+      <c r="A135" s="44" t="s">
         <v>56</v>
       </c>
       <c r="B135" s="4" t="s">
@@ -8031,7 +8044,7 @@
       </c>
     </row>
     <row r="136" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A136" s="43" t="s">
+      <c r="A136" s="44" t="s">
         <v>56</v>
       </c>
       <c r="B136" s="4" t="s">
@@ -8069,7 +8082,7 @@
       </c>
     </row>
     <row r="137" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A137" s="43" t="s">
+      <c r="A137" s="44" t="s">
         <v>57</v>
       </c>
       <c r="B137" s="4" t="s">
@@ -8107,7 +8120,7 @@
       </c>
     </row>
     <row r="138" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A138" s="43" t="s">
+      <c r="A138" s="44" t="s">
         <v>57</v>
       </c>
       <c r="B138" s="4" t="s">
@@ -8145,7 +8158,7 @@
       </c>
     </row>
     <row r="139" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A139" s="43" t="s">
+      <c r="A139" s="44" t="s">
         <v>57</v>
       </c>
       <c r="B139" s="4" t="s">
@@ -8183,7 +8196,7 @@
       </c>
     </row>
     <row r="140" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A140" s="43" t="s">
+      <c r="A140" s="44" t="s">
         <v>57</v>
       </c>
       <c r="B140" s="4" t="s">
@@ -8259,7 +8272,7 @@
       </c>
     </row>
     <row r="142" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A142" s="43" t="s">
+      <c r="A142" s="44" t="s">
         <v>59</v>
       </c>
       <c r="B142" s="4" t="s">
@@ -8297,7 +8310,7 @@
       </c>
     </row>
     <row r="143" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A143" s="43" t="s">
+      <c r="A143" s="44" t="s">
         <v>59</v>
       </c>
       <c r="B143" s="4" t="s">
@@ -8335,7 +8348,7 @@
       </c>
     </row>
     <row r="144" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A144" s="43" t="s">
+      <c r="A144" s="44" t="s">
         <v>59</v>
       </c>
       <c r="B144" s="4" t="s">
@@ -8373,7 +8386,7 @@
       </c>
     </row>
     <row r="145" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A145" s="43" t="s">
+      <c r="A145" s="44" t="s">
         <v>59</v>
       </c>
       <c r="B145" s="4" t="s">
@@ -8401,7 +8414,7 @@
       </c>
     </row>
     <row r="146" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A146" s="43" t="s">
+      <c r="A146" s="44" t="s">
         <v>60</v>
       </c>
       <c r="B146" s="4" t="s">
@@ -8439,7 +8452,7 @@
       </c>
     </row>
     <row r="147" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A147" s="43" t="s">
+      <c r="A147" s="44" t="s">
         <v>60</v>
       </c>
       <c r="B147" s="4" t="s">
@@ -8477,7 +8490,7 @@
       </c>
     </row>
     <row r="148" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A148" s="43" t="s">
+      <c r="A148" s="44" t="s">
         <v>60</v>
       </c>
       <c r="B148" s="4" t="s">
@@ -8515,7 +8528,7 @@
       </c>
     </row>
     <row r="149" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A149" s="43" t="s">
+      <c r="A149" s="44" t="s">
         <v>60</v>
       </c>
       <c r="B149" s="4" t="s">
@@ -8553,7 +8566,7 @@
       </c>
     </row>
     <row r="150" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A150" s="43" t="s">
+      <c r="A150" s="44" t="s">
         <v>61</v>
       </c>
       <c r="B150" s="4" t="s">
@@ -8591,7 +8604,7 @@
       </c>
     </row>
     <row r="151" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A151" s="43" t="s">
+      <c r="A151" s="44" t="s">
         <v>61</v>
       </c>
       <c r="B151" s="4" t="s">
@@ -8629,7 +8642,7 @@
       </c>
     </row>
     <row r="152" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A152" s="43" t="s">
+      <c r="A152" s="44" t="s">
         <v>61</v>
       </c>
       <c r="B152" s="4" t="s">
@@ -8667,7 +8680,7 @@
       </c>
     </row>
     <row r="153" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A153" s="43" t="s">
+      <c r="A153" s="44" t="s">
         <v>62</v>
       </c>
       <c r="B153" s="4" t="s">
@@ -8705,7 +8718,7 @@
       </c>
     </row>
     <row r="154" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A154" s="43" t="s">
+      <c r="A154" s="44" t="s">
         <v>62</v>
       </c>
       <c r="B154" s="4" t="s">
@@ -8743,7 +8756,7 @@
       </c>
     </row>
     <row r="155" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A155" s="43" t="s">
+      <c r="A155" s="44" t="s">
         <v>62</v>
       </c>
       <c r="B155" s="4" t="s">
@@ -8781,7 +8794,7 @@
       </c>
     </row>
     <row r="156" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A156" s="43" t="s">
+      <c r="A156" s="44" t="s">
         <v>62</v>
       </c>
       <c r="B156" s="4" t="s">
@@ -8819,7 +8832,7 @@
       </c>
     </row>
     <row r="157" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A157" s="43" t="s">
+      <c r="A157" s="44" t="s">
         <v>63</v>
       </c>
       <c r="B157" s="4" t="s">
@@ -8845,7 +8858,7 @@
       </c>
     </row>
     <row r="158" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A158" s="43" t="s">
+      <c r="A158" s="44" t="s">
         <v>63</v>
       </c>
       <c r="B158" s="4" t="s">
@@ -8871,7 +8884,7 @@
       </c>
     </row>
     <row r="159" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A159" s="43" t="s">
+      <c r="A159" s="44" t="s">
         <v>63</v>
       </c>
       <c r="B159" s="4" t="s">
@@ -8899,7 +8912,7 @@
       </c>
     </row>
     <row r="160" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A160" s="43" t="s">
+      <c r="A160" s="44" t="s">
         <v>63</v>
       </c>
       <c r="B160" s="4" t="s">
@@ -8927,7 +8940,7 @@
       </c>
     </row>
     <row r="161" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A161" s="43" t="s">
+      <c r="A161" s="44" t="s">
         <v>64</v>
       </c>
       <c r="B161" s="4" t="s">
@@ -8945,7 +8958,7 @@
       <c r="L161" s="6"/>
     </row>
     <row r="162" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A162" s="43" t="s">
+      <c r="A162" s="44" t="s">
         <v>64</v>
       </c>
       <c r="B162" s="4" t="s">
@@ -8963,7 +8976,7 @@
       <c r="L162" s="6"/>
     </row>
     <row r="163" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A163" s="43" t="s">
+      <c r="A163" s="44" t="s">
         <v>64</v>
       </c>
       <c r="B163" s="4" t="s">
@@ -8983,7 +8996,7 @@
       <c r="L163" s="6"/>
     </row>
     <row r="164" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A164" s="43" t="s">
+      <c r="A164" s="44" t="s">
         <v>65</v>
       </c>
       <c r="B164" s="4" t="s">
@@ -9011,7 +9024,7 @@
       </c>
     </row>
     <row r="165" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A165" s="43" t="s">
+      <c r="A165" s="44" t="s">
         <v>65</v>
       </c>
       <c r="B165" s="4" t="s">
@@ -9049,7 +9062,7 @@
       </c>
     </row>
     <row r="166" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A166" s="43" t="s">
+      <c r="A166" s="44" t="s">
         <v>65</v>
       </c>
       <c r="B166" s="4" t="s">
@@ -9087,7 +9100,7 @@
       </c>
     </row>
     <row r="167" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A167" s="43" t="s">
+      <c r="A167" s="44" t="s">
         <v>65</v>
       </c>
       <c r="B167" s="4" t="s">
@@ -9125,7 +9138,7 @@
       </c>
     </row>
     <row r="168" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A168" s="43" t="s">
+      <c r="A168" s="44" t="s">
         <v>66</v>
       </c>
       <c r="B168" s="4" t="s">
@@ -9143,7 +9156,7 @@
       <c r="L168" s="6"/>
     </row>
     <row r="169" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A169" s="43" t="s">
+      <c r="A169" s="44" t="s">
         <v>66</v>
       </c>
       <c r="B169" s="4" t="s">
@@ -9181,7 +9194,7 @@
       </c>
     </row>
     <row r="170" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A170" s="43" t="s">
+      <c r="A170" s="44" t="s">
         <v>66</v>
       </c>
       <c r="B170" s="4" t="s">
@@ -9219,7 +9232,7 @@
       </c>
     </row>
     <row r="171" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A171" s="43" t="s">
+      <c r="A171" s="44" t="s">
         <v>66</v>
       </c>
       <c r="B171" s="4" t="s">
@@ -9257,7 +9270,7 @@
       </c>
     </row>
     <row r="172" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A172" s="43" t="s">
+      <c r="A172" s="44" t="s">
         <v>66</v>
       </c>
       <c r="B172" s="4" t="s">
@@ -9295,7 +9308,7 @@
       </c>
     </row>
     <row r="173" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A173" s="43" t="s">
+      <c r="A173" s="44" t="s">
         <v>67</v>
       </c>
       <c r="B173" s="4" t="s">
@@ -9333,7 +9346,7 @@
       </c>
     </row>
     <row r="174" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A174" s="43" t="s">
+      <c r="A174" s="44" t="s">
         <v>67</v>
       </c>
       <c r="B174" s="4" t="s">
@@ -9351,7 +9364,7 @@
       <c r="L174" s="6"/>
     </row>
     <row r="175" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A175" s="43" t="s">
+      <c r="A175" s="44" t="s">
         <v>67</v>
       </c>
       <c r="B175" s="4" t="s">
@@ -9369,7 +9382,7 @@
       <c r="L175" s="6"/>
     </row>
     <row r="176" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A176" s="43" t="s">
+      <c r="A176" s="44" t="s">
         <v>68</v>
       </c>
       <c r="B176" s="4" t="s">
@@ -9407,7 +9420,7 @@
       </c>
     </row>
     <row r="177" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A177" s="43" t="s">
+      <c r="A177" s="44" t="s">
         <v>68</v>
       </c>
       <c r="B177" s="4" t="s">
@@ -9439,7 +9452,7 @@
       <c r="L177" s="6"/>
     </row>
     <row r="178" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A178" s="43" t="s">
+      <c r="A178" s="44" t="s">
         <v>68</v>
       </c>
       <c r="B178" s="4" t="s">
@@ -9477,7 +9490,7 @@
       </c>
     </row>
     <row r="179" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A179" s="43" t="s">
+      <c r="A179" s="44" t="s">
         <v>69</v>
       </c>
       <c r="B179" s="4" t="s">
@@ -9515,7 +9528,7 @@
       </c>
     </row>
     <row r="180" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A180" s="43" t="s">
+      <c r="A180" s="44" t="s">
         <v>69</v>
       </c>
       <c r="B180" s="4" t="s">
@@ -9541,7 +9554,7 @@
       <c r="L180" s="6"/>
     </row>
     <row r="181" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A181" s="43" t="s">
+      <c r="A181" s="44" t="s">
         <v>69</v>
       </c>
       <c r="B181" s="4" t="s">
@@ -9579,7 +9592,7 @@
       </c>
     </row>
     <row r="182" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A182" s="43" t="s">
+      <c r="A182" s="44" t="s">
         <v>70</v>
       </c>
       <c r="B182" s="4" t="s">
@@ -9597,7 +9610,7 @@
       <c r="L182" s="6"/>
     </row>
     <row r="183" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A183" s="43" t="s">
+      <c r="A183" s="44" t="s">
         <v>70</v>
       </c>
       <c r="B183" s="4" t="s">
@@ -9615,7 +9628,7 @@
       <c r="L183" s="6"/>
     </row>
     <row r="184" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A184" s="43" t="s">
+      <c r="A184" s="44" t="s">
         <v>70</v>
       </c>
       <c r="B184" s="4" t="s">
@@ -9633,7 +9646,7 @@
       <c r="L184" s="6"/>
     </row>
     <row r="185" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A185" s="43" t="s">
+      <c r="A185" s="44" t="s">
         <v>70</v>
       </c>
       <c r="B185" s="4" t="s">
@@ -9651,7 +9664,7 @@
       <c r="L185" s="6"/>
     </row>
     <row r="186" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A186" s="43" t="s">
+      <c r="A186" s="44" t="s">
         <v>70</v>
       </c>
       <c r="B186" s="4" t="s">
@@ -9669,7 +9682,7 @@
       <c r="L186" s="6"/>
     </row>
     <row r="187" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A187" s="43" t="s">
+      <c r="A187" s="44" t="s">
         <v>71</v>
       </c>
       <c r="B187" s="4" t="s">
@@ -9687,7 +9700,7 @@
       <c r="L187" s="6"/>
     </row>
     <row r="188" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A188" s="43" t="s">
+      <c r="A188" s="44" t="s">
         <v>71</v>
       </c>
       <c r="B188" s="4" t="s">
@@ -9725,7 +9738,7 @@
       </c>
     </row>
     <row r="189" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A189" s="43" t="s">
+      <c r="A189" s="44" t="s">
         <v>71</v>
       </c>
       <c r="B189" s="4" t="s">
@@ -9763,7 +9776,7 @@
       </c>
     </row>
     <row r="190" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A190" s="43" t="s">
+      <c r="A190" s="44" t="s">
         <v>71</v>
       </c>
       <c r="B190" s="4" t="s">
@@ -9789,7 +9802,7 @@
       <c r="L190" s="6"/>
     </row>
     <row r="191" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A191" s="43" t="s">
+      <c r="A191" s="44" t="s">
         <v>71</v>
       </c>
       <c r="B191" s="4" t="s">
@@ -9827,7 +9840,7 @@
       </c>
     </row>
     <row r="192" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A192" s="43" t="s">
+      <c r="A192" s="44" t="s">
         <v>72</v>
       </c>
       <c r="B192" s="4" t="s">
@@ -9845,7 +9858,7 @@
       <c r="L192" s="6"/>
     </row>
     <row r="193" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A193" s="43" t="s">
+      <c r="A193" s="44" t="s">
         <v>72</v>
       </c>
       <c r="B193" s="4" t="s">
@@ -9883,7 +9896,7 @@
       </c>
     </row>
     <row r="194" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A194" s="43" t="s">
+      <c r="A194" s="44" t="s">
         <v>72</v>
       </c>
       <c r="B194" s="4" t="s">
@@ -9913,7 +9926,7 @@
       <c r="L194" s="6"/>
     </row>
     <row r="195" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A195" s="43" t="s">
+      <c r="A195" s="44" t="s">
         <v>72</v>
       </c>
       <c r="B195" s="4" t="s">
@@ -9951,7 +9964,7 @@
       </c>
     </row>
     <row r="196" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A196" s="43" t="s">
+      <c r="A196" s="44" t="s">
         <v>73</v>
       </c>
       <c r="B196" s="4" t="s">
@@ -9989,7 +10002,7 @@
       </c>
     </row>
     <row r="197" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A197" s="43" t="s">
+      <c r="A197" s="44" t="s">
         <v>73</v>
       </c>
       <c r="B197" s="4" t="s">
@@ -10007,7 +10020,7 @@
       <c r="L197" s="6"/>
     </row>
     <row r="198" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A198" s="43" t="s">
+      <c r="A198" s="44" t="s">
         <v>73</v>
       </c>
       <c r="B198" s="4" t="s">
@@ -10045,7 +10058,7 @@
       </c>
     </row>
     <row r="199" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A199" s="43" t="s">
+      <c r="A199" s="44" t="s">
         <v>74</v>
       </c>
       <c r="B199" s="4" t="s">
@@ -10083,7 +10096,7 @@
       </c>
     </row>
     <row r="200" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A200" s="43" t="s">
+      <c r="A200" s="44" t="s">
         <v>74</v>
       </c>
       <c r="B200" s="4" t="s">
@@ -10121,7 +10134,7 @@
       </c>
     </row>
     <row r="201" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A201" s="43" t="s">
+      <c r="A201" s="44" t="s">
         <v>74</v>
       </c>
       <c r="B201" s="4" t="s">
@@ -10159,7 +10172,7 @@
       </c>
     </row>
     <row r="202" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A202" s="43" t="s">
+      <c r="A202" s="44" t="s">
         <v>74</v>
       </c>
       <c r="B202" s="4" t="s">
@@ -10197,7 +10210,7 @@
       </c>
     </row>
     <row r="203" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A203" s="43" t="s">
+      <c r="A203" s="44" t="s">
         <v>74</v>
       </c>
       <c r="B203" s="4" t="s">
@@ -14293,12 +14306,40 @@
     </filterColumn>
   </autoFilter>
   <mergeCells count="52">
-    <mergeCell ref="A28:A30"/>
-    <mergeCell ref="A2:A6"/>
-    <mergeCell ref="A7:A10"/>
-    <mergeCell ref="A11:A14"/>
-    <mergeCell ref="A17:A21"/>
-    <mergeCell ref="A22:A26"/>
+    <mergeCell ref="A187:A191"/>
+    <mergeCell ref="A192:A195"/>
+    <mergeCell ref="A196:A198"/>
+    <mergeCell ref="A199:A203"/>
+    <mergeCell ref="A164:A167"/>
+    <mergeCell ref="A168:A172"/>
+    <mergeCell ref="A173:A175"/>
+    <mergeCell ref="A176:A178"/>
+    <mergeCell ref="A179:A181"/>
+    <mergeCell ref="A182:A186"/>
+    <mergeCell ref="A161:A163"/>
+    <mergeCell ref="A120:A122"/>
+    <mergeCell ref="A123:A125"/>
+    <mergeCell ref="A126:A129"/>
+    <mergeCell ref="A130:A134"/>
+    <mergeCell ref="A135:A136"/>
+    <mergeCell ref="A137:A140"/>
+    <mergeCell ref="A142:A145"/>
+    <mergeCell ref="A146:A149"/>
+    <mergeCell ref="A150:A152"/>
+    <mergeCell ref="A153:A156"/>
+    <mergeCell ref="A157:A160"/>
+    <mergeCell ref="A114:A118"/>
+    <mergeCell ref="A75:A76"/>
+    <mergeCell ref="A78:A81"/>
+    <mergeCell ref="A82:A85"/>
+    <mergeCell ref="A86:A89"/>
+    <mergeCell ref="A90:A94"/>
+    <mergeCell ref="A95:A97"/>
+    <mergeCell ref="A98:A100"/>
+    <mergeCell ref="A101:A103"/>
+    <mergeCell ref="A104:A106"/>
+    <mergeCell ref="A107:A109"/>
+    <mergeCell ref="A110:A113"/>
     <mergeCell ref="A70:A74"/>
     <mergeCell ref="A31:A33"/>
     <mergeCell ref="A34:A36"/>
@@ -14311,40 +14352,12 @@
     <mergeCell ref="A58:A61"/>
     <mergeCell ref="A62:A64"/>
     <mergeCell ref="A65:A69"/>
-    <mergeCell ref="A114:A118"/>
-    <mergeCell ref="A75:A76"/>
-    <mergeCell ref="A78:A81"/>
-    <mergeCell ref="A82:A85"/>
-    <mergeCell ref="A86:A89"/>
-    <mergeCell ref="A90:A94"/>
-    <mergeCell ref="A95:A97"/>
-    <mergeCell ref="A98:A100"/>
-    <mergeCell ref="A101:A103"/>
-    <mergeCell ref="A104:A106"/>
-    <mergeCell ref="A107:A109"/>
-    <mergeCell ref="A110:A113"/>
-    <mergeCell ref="A161:A163"/>
-    <mergeCell ref="A120:A122"/>
-    <mergeCell ref="A123:A125"/>
-    <mergeCell ref="A126:A129"/>
-    <mergeCell ref="A130:A134"/>
-    <mergeCell ref="A135:A136"/>
-    <mergeCell ref="A137:A140"/>
-    <mergeCell ref="A142:A145"/>
-    <mergeCell ref="A146:A149"/>
-    <mergeCell ref="A150:A152"/>
-    <mergeCell ref="A153:A156"/>
-    <mergeCell ref="A157:A160"/>
-    <mergeCell ref="A187:A191"/>
-    <mergeCell ref="A192:A195"/>
-    <mergeCell ref="A196:A198"/>
-    <mergeCell ref="A199:A203"/>
-    <mergeCell ref="A164:A167"/>
-    <mergeCell ref="A168:A172"/>
-    <mergeCell ref="A173:A175"/>
-    <mergeCell ref="A176:A178"/>
-    <mergeCell ref="A179:A181"/>
-    <mergeCell ref="A182:A186"/>
+    <mergeCell ref="A28:A30"/>
+    <mergeCell ref="A2:A6"/>
+    <mergeCell ref="A7:A10"/>
+    <mergeCell ref="A11:A14"/>
+    <mergeCell ref="A17:A21"/>
+    <mergeCell ref="A22:A26"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -18566,10 +18579,10 @@
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B19" s="26" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="C19" s="26" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
     </row>
   </sheetData>
@@ -18580,20 +18593,19 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DF17EB8-02F1-485E-9D81-51CF2F0BE0EA}">
-  <dimension ref="A1:P44"/>
+  <dimension ref="A1:O44"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.28515625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="22" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="15.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="11" width="12.7109375" customWidth="1"/>
-    <col min="12" max="12" width="11.5703125" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="12.140625" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="11.28515625" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="10.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B1" s="36">
         <v>1</v>
       </c>
@@ -18624,23 +18636,17 @@
       <c r="K1" s="36">
         <v>10</v>
       </c>
-      <c r="L1" s="36">
-        <v>11</v>
-      </c>
-      <c r="M1" s="36">
-        <v>12</v>
-      </c>
-      <c r="N1" s="36">
-        <v>13</v>
-      </c>
-      <c r="O1" s="36">
-        <v>14</v>
-      </c>
-      <c r="P1" s="36">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="M1" t="s">
+        <v>171</v>
+      </c>
+      <c r="N1" t="s">
+        <v>170</v>
+      </c>
+      <c r="O1" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>123</v>
       </c>
@@ -18674,28 +18680,20 @@
       <c r="K2" s="37">
         <v>19900000</v>
       </c>
-      <c r="L2" s="37">
-        <f>AVERAGE(J2:K2)</f>
-        <v>19750000</v>
-      </c>
-      <c r="M2" s="37">
-        <f t="shared" ref="M2:P2" si="0">AVERAGE(K2:L2)</f>
-        <v>19825000</v>
-      </c>
-      <c r="N2" s="37">
-        <f t="shared" si="0"/>
-        <v>19787500</v>
-      </c>
-      <c r="O2" s="37">
-        <f t="shared" si="0"/>
-        <v>19806250</v>
-      </c>
-      <c r="P2" s="37">
-        <f t="shared" si="0"/>
-        <v>19796875</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="M2" s="41">
+        <f t="shared" ref="M2:M7" si="0">0.8*N2</f>
+        <v>148480000</v>
+      </c>
+      <c r="N2" s="41">
+        <f>+SUM(B2:K2)</f>
+        <v>185600000</v>
+      </c>
+      <c r="O2" s="41">
+        <f t="shared" ref="O2:O7" si="1">+N2*1.2</f>
+        <v>222720000</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>140</v>
       </c>
@@ -18729,28 +18727,20 @@
       <c r="K3" s="37">
         <v>25400000</v>
       </c>
-      <c r="L3" s="37">
-        <f t="shared" ref="L3:L18" si="1">AVERAGE(J3:K3)</f>
-        <v>25250000</v>
-      </c>
-      <c r="M3" s="37">
-        <f t="shared" ref="M3:M18" si="2">AVERAGE(K3:L3)</f>
-        <v>25325000</v>
-      </c>
-      <c r="N3" s="37">
-        <f t="shared" ref="N3:N18" si="3">AVERAGE(L3:M3)</f>
-        <v>25287500</v>
-      </c>
-      <c r="O3" s="37">
-        <f t="shared" ref="O3:O18" si="4">AVERAGE(M3:N3)</f>
-        <v>25306250</v>
-      </c>
-      <c r="P3" s="37">
-        <f t="shared" ref="P3:P18" si="5">AVERAGE(N3:O3)</f>
-        <v>25296875</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="M3" s="41">
+        <f>0.8*N3</f>
+        <v>201600000</v>
+      </c>
+      <c r="N3" s="41">
+        <f>+SUM(B3:K3)</f>
+        <v>252000000</v>
+      </c>
+      <c r="O3" s="41">
+        <f t="shared" si="1"/>
+        <v>302400000</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>141</v>
       </c>
@@ -18784,28 +18774,20 @@
       <c r="K4" s="38">
         <v>8200000</v>
       </c>
-      <c r="L4" s="37">
+      <c r="M4" s="41">
+        <f t="shared" si="0"/>
+        <v>66480000</v>
+      </c>
+      <c r="N4" s="41">
+        <f>+SUM(B4:K4)</f>
+        <v>83100000</v>
+      </c>
+      <c r="O4" s="41">
         <f t="shared" si="1"/>
-        <v>8200000</v>
-      </c>
-      <c r="M4" s="37">
-        <f t="shared" si="2"/>
-        <v>8200000</v>
-      </c>
-      <c r="N4" s="37">
-        <f t="shared" si="3"/>
-        <v>8200000</v>
-      </c>
-      <c r="O4" s="37">
-        <f t="shared" si="4"/>
-        <v>8200000</v>
-      </c>
-      <c r="P4" s="37">
-        <f t="shared" si="5"/>
-        <v>8200000</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+        <v>99720000</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>142</v>
       </c>
@@ -18839,28 +18821,20 @@
       <c r="K5" s="38">
         <v>41300000</v>
       </c>
-      <c r="L5" s="37">
+      <c r="M5" s="41">
+        <f t="shared" si="0"/>
+        <v>322000000</v>
+      </c>
+      <c r="N5" s="41">
+        <f>+SUM(B5:K5)</f>
+        <v>402500000</v>
+      </c>
+      <c r="O5" s="41">
         <f t="shared" si="1"/>
-        <v>41250000</v>
-      </c>
-      <c r="M5" s="37">
-        <f t="shared" si="2"/>
-        <v>41275000</v>
-      </c>
-      <c r="N5" s="37">
-        <f t="shared" si="3"/>
-        <v>41262500</v>
-      </c>
-      <c r="O5" s="37">
-        <f t="shared" si="4"/>
-        <v>41268750</v>
-      </c>
-      <c r="P5" s="37">
-        <f t="shared" si="5"/>
-        <v>41265625</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+        <v>483000000</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>143</v>
       </c>
@@ -18894,28 +18868,20 @@
       <c r="K6" s="37">
         <v>13300000</v>
       </c>
-      <c r="L6" s="37">
+      <c r="M6" s="41">
+        <f t="shared" si="0"/>
+        <v>99120000</v>
+      </c>
+      <c r="N6" s="41">
+        <f>+SUM(B6:K6)</f>
+        <v>123900000</v>
+      </c>
+      <c r="O6" s="41">
         <f t="shared" si="1"/>
-        <v>13200000</v>
-      </c>
-      <c r="M6" s="37">
-        <f t="shared" si="2"/>
-        <v>13250000</v>
-      </c>
-      <c r="N6" s="37">
-        <f t="shared" si="3"/>
-        <v>13225000</v>
-      </c>
-      <c r="O6" s="37">
-        <f t="shared" si="4"/>
-        <v>13237500</v>
-      </c>
-      <c r="P6" s="37">
-        <f t="shared" si="5"/>
-        <v>13231250</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+        <v>148680000</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>144</v>
       </c>
@@ -18949,28 +18915,20 @@
       <c r="K7" s="37">
         <v>158400000</v>
       </c>
-      <c r="L7" s="37">
+      <c r="M7" s="41">
+        <f t="shared" si="0"/>
+        <v>1230800000</v>
+      </c>
+      <c r="N7" s="41">
+        <f t="shared" ref="N7:N18" si="2">+SUM(B7:K7)</f>
+        <v>1538500000</v>
+      </c>
+      <c r="O7" s="41">
         <f t="shared" si="1"/>
-        <v>153850000</v>
-      </c>
-      <c r="M7" s="37">
-        <f t="shared" si="2"/>
-        <v>156125000</v>
-      </c>
-      <c r="N7" s="37">
-        <f t="shared" si="3"/>
-        <v>154987500</v>
-      </c>
-      <c r="O7" s="37">
-        <f t="shared" si="4"/>
-        <v>155556250</v>
-      </c>
-      <c r="P7" s="37">
-        <f t="shared" si="5"/>
-        <v>155271875</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+        <v>1846200000</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>145</v>
       </c>
@@ -19004,28 +18962,20 @@
       <c r="K8" s="38">
         <v>0</v>
       </c>
-      <c r="L8" s="37">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="M8" s="37">
+      <c r="M8" s="41">
+        <f t="shared" ref="M8:M18" si="3">0.8*N8</f>
+        <v>64000</v>
+      </c>
+      <c r="N8" s="41">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="N8" s="37">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="O8" s="37">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="P8" s="37">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+        <v>80000</v>
+      </c>
+      <c r="O8" s="41">
+        <f t="shared" ref="O8:O18" si="4">+N8*1.2</f>
+        <v>96000</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>116</v>
       </c>
@@ -19059,28 +19009,20 @@
       <c r="K9" s="37">
         <v>2069100000</v>
       </c>
-      <c r="L9" s="37">
-        <f t="shared" si="1"/>
-        <v>2058175000</v>
-      </c>
-      <c r="M9" s="37">
+      <c r="M9" s="41">
+        <f t="shared" si="3"/>
+        <v>16628800000</v>
+      </c>
+      <c r="N9" s="41">
         <f t="shared" si="2"/>
-        <v>2063637500</v>
-      </c>
-      <c r="N9" s="37">
-        <f t="shared" si="3"/>
-        <v>2060906250</v>
-      </c>
-      <c r="O9" s="37">
+        <v>20786000000</v>
+      </c>
+      <c r="O9" s="41">
         <f t="shared" si="4"/>
-        <v>2062271875</v>
-      </c>
-      <c r="P9" s="37">
-        <f t="shared" si="5"/>
-        <v>2061589062.5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+        <v>24943200000</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>146</v>
       </c>
@@ -19114,28 +19056,20 @@
       <c r="K10" s="37">
         <v>8200000</v>
       </c>
-      <c r="L10" s="37">
-        <f t="shared" si="1"/>
-        <v>8200000</v>
-      </c>
-      <c r="M10" s="37">
+      <c r="M10" s="41">
+        <f t="shared" si="3"/>
+        <v>66480000</v>
+      </c>
+      <c r="N10" s="41">
         <f t="shared" si="2"/>
-        <v>8200000</v>
-      </c>
-      <c r="N10" s="37">
-        <f t="shared" si="3"/>
-        <v>8200000</v>
-      </c>
-      <c r="O10" s="37">
+        <v>83100000</v>
+      </c>
+      <c r="O10" s="41">
         <f t="shared" si="4"/>
-        <v>8200000</v>
-      </c>
-      <c r="P10" s="37">
-        <f t="shared" si="5"/>
-        <v>8200000</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+        <v>99720000</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>147</v>
       </c>
@@ -19169,28 +19103,20 @@
       <c r="K11" s="37">
         <v>82300000</v>
       </c>
-      <c r="L11" s="37">
-        <f t="shared" si="1"/>
-        <v>81750000</v>
-      </c>
-      <c r="M11" s="37">
+      <c r="M11" s="41">
+        <f t="shared" si="3"/>
+        <v>627920000</v>
+      </c>
+      <c r="N11" s="41">
         <f t="shared" si="2"/>
-        <v>82025000</v>
-      </c>
-      <c r="N11" s="37">
-        <f t="shared" si="3"/>
-        <v>81887500</v>
-      </c>
-      <c r="O11" s="37">
+        <v>784900000</v>
+      </c>
+      <c r="O11" s="41">
         <f t="shared" si="4"/>
-        <v>81956250</v>
-      </c>
-      <c r="P11" s="37">
-        <f t="shared" si="5"/>
-        <v>81921875</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+        <v>941880000</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>148</v>
       </c>
@@ -19224,28 +19150,20 @@
       <c r="K12" s="37">
         <v>5700000</v>
       </c>
-      <c r="L12" s="37">
-        <f t="shared" si="1"/>
-        <v>5600000</v>
-      </c>
-      <c r="M12" s="37">
+      <c r="M12" s="41">
+        <f t="shared" si="3"/>
+        <v>58720000</v>
+      </c>
+      <c r="N12" s="41">
         <f t="shared" si="2"/>
-        <v>5650000</v>
-      </c>
-      <c r="N12" s="37">
-        <f t="shared" si="3"/>
-        <v>5625000</v>
-      </c>
-      <c r="O12" s="37">
+        <v>73400000</v>
+      </c>
+      <c r="O12" s="41">
         <f t="shared" si="4"/>
-        <v>5637500</v>
-      </c>
-      <c r="P12" s="37">
-        <f t="shared" si="5"/>
-        <v>5631250</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+        <v>88080000</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>149</v>
       </c>
@@ -19279,28 +19197,20 @@
       <c r="K13" s="37">
         <v>21500000</v>
       </c>
-      <c r="L13" s="37">
-        <f t="shared" si="1"/>
-        <v>21450000</v>
-      </c>
-      <c r="M13" s="37">
+      <c r="M13" s="41">
+        <f t="shared" si="3"/>
+        <v>172160000</v>
+      </c>
+      <c r="N13" s="41">
         <f t="shared" si="2"/>
-        <v>21475000</v>
-      </c>
-      <c r="N13" s="37">
-        <f t="shared" si="3"/>
-        <v>21462500</v>
-      </c>
-      <c r="O13" s="37">
+        <v>215200000</v>
+      </c>
+      <c r="O13" s="41">
         <f t="shared" si="4"/>
-        <v>21468750</v>
-      </c>
-      <c r="P13" s="37">
-        <f t="shared" si="5"/>
-        <v>21465625</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
+        <v>258240000</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>156</v>
       </c>
@@ -19334,28 +19244,20 @@
       <c r="K14" s="37">
         <v>7900000</v>
       </c>
-      <c r="L14" s="37">
-        <f t="shared" si="1"/>
-        <v>7850000</v>
-      </c>
-      <c r="M14" s="37">
+      <c r="M14" s="41">
+        <f t="shared" si="3"/>
+        <v>59760000</v>
+      </c>
+      <c r="N14" s="41">
         <f t="shared" si="2"/>
-        <v>7875000</v>
-      </c>
-      <c r="N14" s="37">
-        <f t="shared" si="3"/>
-        <v>7862500</v>
-      </c>
-      <c r="O14" s="37">
+        <v>74700000</v>
+      </c>
+      <c r="O14" s="41">
         <f t="shared" si="4"/>
-        <v>7868750</v>
-      </c>
-      <c r="P14" s="37">
-        <f t="shared" si="5"/>
-        <v>7865625</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
+        <v>89640000</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>150</v>
       </c>
@@ -19389,28 +19291,20 @@
       <c r="K15" s="37">
         <v>123300000</v>
       </c>
-      <c r="L15" s="37">
-        <f t="shared" si="1"/>
-        <v>122850000</v>
-      </c>
-      <c r="M15" s="37">
+      <c r="M15" s="41">
+        <f t="shared" si="3"/>
+        <v>983840000</v>
+      </c>
+      <c r="N15" s="41">
         <f t="shared" si="2"/>
-        <v>123075000</v>
-      </c>
-      <c r="N15" s="37">
-        <f t="shared" si="3"/>
-        <v>122962500</v>
-      </c>
-      <c r="O15" s="37">
+        <v>1229800000</v>
+      </c>
+      <c r="O15" s="41">
         <f t="shared" si="4"/>
-        <v>123018750</v>
-      </c>
-      <c r="P15" s="37">
-        <f t="shared" si="5"/>
-        <v>122990625</v>
-      </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
+        <v>1475760000</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>151</v>
       </c>
@@ -19444,32 +19338,24 @@
       <c r="K16" s="37">
         <v>128200000</v>
       </c>
-      <c r="L16" s="37">
-        <f t="shared" si="1"/>
-        <v>127800000</v>
-      </c>
-      <c r="M16" s="37">
+      <c r="M16" s="41">
+        <f t="shared" si="3"/>
+        <v>1000080000</v>
+      </c>
+      <c r="N16" s="41">
         <f t="shared" si="2"/>
-        <v>128000000</v>
-      </c>
-      <c r="N16" s="37">
-        <f t="shared" si="3"/>
-        <v>127900000</v>
-      </c>
-      <c r="O16" s="37">
+        <v>1250100000</v>
+      </c>
+      <c r="O16" s="41">
         <f t="shared" si="4"/>
-        <v>127950000</v>
-      </c>
-      <c r="P16" s="37">
-        <f t="shared" si="5"/>
-        <v>127925000</v>
-      </c>
-    </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
+        <v>1500120000</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>152</v>
       </c>
-      <c r="B17" s="41">
+      <c r="B17" s="42">
         <v>969375250</v>
       </c>
       <c r="C17">
@@ -19499,28 +19385,20 @@
       <c r="K17">
         <v>1055564000</v>
       </c>
-      <c r="L17" s="37">
-        <f t="shared" si="1"/>
-        <v>1041846000</v>
-      </c>
-      <c r="M17" s="37">
+      <c r="M17" s="41">
+        <f t="shared" si="3"/>
+        <v>8241196800</v>
+      </c>
+      <c r="N17" s="41">
         <f t="shared" si="2"/>
-        <v>1048705000</v>
-      </c>
-      <c r="N17" s="37">
-        <f t="shared" si="3"/>
-        <v>1045275500</v>
-      </c>
-      <c r="O17" s="37">
+        <v>10301496000</v>
+      </c>
+      <c r="O17" s="41">
         <f t="shared" si="4"/>
-        <v>1046990250</v>
-      </c>
-      <c r="P17" s="37">
-        <f t="shared" si="5"/>
-        <v>1046132875</v>
-      </c>
-    </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
+        <v>12361795200</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>153</v>
       </c>
@@ -19554,28 +19432,20 @@
       <c r="K18" s="25">
         <v>1000000</v>
       </c>
-      <c r="L18" s="37">
-        <f t="shared" si="1"/>
-        <v>950000</v>
-      </c>
-      <c r="M18" s="37">
+      <c r="M18" s="41">
+        <f t="shared" si="3"/>
+        <v>9840000</v>
+      </c>
+      <c r="N18" s="41">
         <f t="shared" si="2"/>
-        <v>975000</v>
-      </c>
-      <c r="N18" s="37">
-        <f t="shared" si="3"/>
-        <v>962500</v>
-      </c>
-      <c r="O18" s="37">
+        <v>12300000</v>
+      </c>
+      <c r="O18" s="41">
         <f t="shared" si="4"/>
-        <v>968750</v>
-      </c>
-      <c r="P18" s="37">
-        <f t="shared" si="5"/>
-        <v>965625</v>
-      </c>
-    </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
+        <v>14760000</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B19" s="25"/>
       <c r="C19" s="25"/>
       <c r="D19" s="25"/>
@@ -19585,42 +19455,53 @@
       <c r="H19" s="25"/>
       <c r="I19" s="25"/>
       <c r="J19" s="25"/>
-    </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="B20" s="42"/>
-      <c r="C20" s="42"/>
-      <c r="D20" s="42"/>
-      <c r="E20" s="42"/>
-      <c r="F20" s="42"/>
-      <c r="G20" s="42"/>
-      <c r="H20" s="42"/>
-      <c r="I20" s="42"/>
-      <c r="J20" s="42"/>
-    </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="B21" s="41"/>
-      <c r="C21" s="41"/>
-      <c r="D21" s="25"/>
+      <c r="K19" s="25"/>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="B20" s="43"/>
+      <c r="C20" s="43"/>
+      <c r="D20" s="43"/>
+      <c r="E20" s="43"/>
+      <c r="F20" s="43"/>
+      <c r="G20" s="43"/>
+      <c r="H20" s="43"/>
+      <c r="I20" s="43"/>
+      <c r="J20" s="43"/>
+      <c r="K20" s="43"/>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="B21" s="43">
+        <v>43365104</v>
+      </c>
+      <c r="C21" s="42"/>
+      <c r="D21" s="42"/>
       <c r="E21" s="25"/>
       <c r="F21" s="25"/>
       <c r="G21" s="25"/>
       <c r="H21" s="25"/>
       <c r="I21" s="25"/>
       <c r="J21" s="25"/>
-    </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="B22" s="41"/>
-      <c r="C22" s="41"/>
-      <c r="D22" s="25"/>
+      <c r="K21" s="25"/>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="B22" s="48">
+        <v>61220888</v>
+      </c>
+      <c r="C22" s="42"/>
+      <c r="D22" s="42"/>
       <c r="E22" s="25"/>
       <c r="F22" s="25"/>
       <c r="G22" s="25"/>
       <c r="H22" s="25"/>
       <c r="I22" s="25"/>
       <c r="J22" s="25"/>
-    </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="B23" s="25"/>
+      <c r="K22" s="25"/>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="B23" s="25">
+        <f>B22+B21</f>
+        <v>104585992</v>
+      </c>
       <c r="C23" s="25"/>
       <c r="D23" s="25"/>
       <c r="E23" s="40"/>
@@ -19631,8 +19512,11 @@
       <c r="J23" s="25"/>
       <c r="K23" s="25"/>
     </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="B24" s="25"/>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="B24" s="25">
+        <f>B16-B23</f>
+        <v>14008</v>
+      </c>
       <c r="C24" s="25"/>
       <c r="D24" s="25"/>
       <c r="E24" s="25"/>
@@ -19643,7 +19527,7 @@
       <c r="J24" s="25"/>
       <c r="K24" s="25"/>
     </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B25" s="25"/>
       <c r="C25" s="25"/>
       <c r="D25" s="25"/>
@@ -19655,7 +19539,7 @@
       <c r="J25" s="25"/>
       <c r="K25" s="25"/>
     </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B26" s="25"/>
       <c r="C26" s="25"/>
       <c r="D26" s="25"/>
@@ -19667,7 +19551,7 @@
       <c r="J26" s="25"/>
       <c r="K26" s="25"/>
     </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B27" s="25"/>
       <c r="C27" s="25"/>
       <c r="D27" s="25"/>
@@ -19679,7 +19563,7 @@
       <c r="J27" s="25"/>
       <c r="K27" s="25"/>
     </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B28" s="25"/>
       <c r="C28" s="25"/>
       <c r="D28" s="25"/>
@@ -19691,7 +19575,7 @@
       <c r="J28" s="25"/>
       <c r="K28" s="25"/>
     </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B29" s="25"/>
       <c r="C29" s="25"/>
       <c r="D29" s="25"/>
@@ -19703,7 +19587,7 @@
       <c r="J29" s="25"/>
       <c r="K29" s="25"/>
     </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B30" s="25"/>
       <c r="C30" s="25"/>
       <c r="D30" s="25"/>
@@ -19715,7 +19599,7 @@
       <c r="J30" s="25"/>
       <c r="K30" s="25"/>
     </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B31" s="25"/>
       <c r="C31" s="25"/>
       <c r="D31" s="25"/>
@@ -19727,7 +19611,7 @@
       <c r="J31" s="25"/>
       <c r="K31" s="25"/>
     </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B32" s="25"/>
       <c r="C32" s="25"/>
       <c r="D32" s="25"/>
@@ -19885,15 +19769,5 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967293" verticalDpi="4294967293" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7AEDCBEC-A12F-4CB4-BD24-1D1201B71C25}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>